--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/purchaseSuggestion.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/purchaseSuggestion.xlsx
@@ -116,7 +116,7 @@
     <t>{.purchaseCost}</t>
   </si>
   <si>
-    <t>{.createTypeName}</t>
+    <t>{.dataTypeName}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -1103,7 +1103,7 @@
     <col min="17" max="17" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" ht="14.25" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>

--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/purchaseSuggestion.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/purchaseSuggestion.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>类型</t>
   </si>
@@ -50,9 +50,6 @@
     <t>系统建议值</t>
   </si>
   <si>
-    <t>物流方式（系统）</t>
-  </si>
-  <si>
     <t>建议采购日期（系统）</t>
   </si>
   <si>
@@ -99,9 +96,6 @@
   </si>
   <si>
     <t>{.suggestPurchaseQty}</t>
-  </si>
-  <si>
-    <t>{.logisticsMethodName}</t>
   </si>
   <si>
     <t>{.suggestPurchaseDate}</t>
@@ -1084,7 +1078,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="21.5" customWidth="1"/>
@@ -1094,16 +1088,15 @@
     <col min="5" max="5" width="9.375" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="16.625" customWidth="1"/>
-    <col min="8" max="8" width="24.875" customWidth="1"/>
-    <col min="9" max="12" width="18.5" customWidth="1"/>
-    <col min="13" max="13" width="17.375" customWidth="1"/>
-    <col min="14" max="14" width="12.5" customWidth="1"/>
-    <col min="15" max="15" width="12.75" customWidth="1"/>
-    <col min="16" max="16" width="13.375" customWidth="1"/>
-    <col min="17" max="17" width="15.375" customWidth="1"/>
+    <col min="8" max="11" width="18.5" customWidth="1"/>
+    <col min="12" max="12" width="17.375" customWidth="1"/>
+    <col min="13" max="13" width="12.5" customWidth="1"/>
+    <col min="14" max="14" width="12.75" customWidth="1"/>
+    <col min="15" max="15" width="13.375" customWidth="1"/>
+    <col min="16" max="16" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:17">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1152,61 +1145,55 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>21</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>23</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>24</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>25</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>26</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>27</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>28</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>29</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>30</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>31</v>
-      </c>
-      <c r="P2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
